--- a/Casos/red_4Nodos/resultados_excel/aleatorio2.xlsx
+++ b/Casos/red_4Nodos/resultados_excel/aleatorio2.xlsx
@@ -5,20 +5,31 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura\OneDrive - Universidad Politécnica de Madrid\optimal_power_flow\github\resultados_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura\OneDrive - Universidad Politécnica de Madrid\optimal_power_flow\github\Casos\red_4Nodos\resultados_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEA848A-A1E7-4069-994F-2AA814D53E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F6CBF2-F044-4A91-8BC9-A4FE2A1CC6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -410,12 +421,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.4140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -423,7 +434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -431,7 +442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -439,7 +450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -447,39 +458,39 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>230.30239996910095</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>230.27799999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>48.542570934172524</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>48.534532239999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7">
-        <v>3688.925225724478</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3600.4802</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
-        <v>4049.6734713417977</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3607.4486999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -487,12 +498,12 @@
         <v>3593.761899146155</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10">
-        <v>201.69226368127434</v>
+        <v>5.1394000000000002</v>
       </c>
     </row>
   </sheetData>
